--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31dc1698d1c34275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c4557d63b9a46c9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c4557d63b9a46c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R48f77d6ffdad4b4f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R48f77d6ffdad4b4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red9ac24081f143bc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red9ac24081f143bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ea678ab8dcd4d23"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ea678ab8dcd4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7e7dda6378c45d0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7e7dda6378c45d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e92765951bb4b4d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e92765951bb4b4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R969f666653dc455a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R969f666653dc455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21de6da28e6a4315"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21de6da28e6a4315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c475bd494c6491d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c475bd494c6491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R50b59f4e9afe4d42"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R50b59f4e9afe4d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2e402b6ca4e4c36"/>
   </x:sheets>
 </x:workbook>
 </file>
